--- a/jpcore-r4/feature/swg2-dental/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
+++ b/jpcore-r4/feature/swg2-dental/StructureDefinition-jp-observation-dentaloral-toothexistence.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3830" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3828" uniqueCount="563">
   <si>
     <t>Property</t>
   </si>
@@ -776,6 +776,9 @@
     <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS</t>
+  </si>
+  <si>
     <t>Coding.system</t>
   </si>
   <si>
@@ -822,6 +825,9 @@
   </si>
   <si>
     <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>procedure</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -975,6 +981,9 @@
     <t>このObservationに関する詳細分類、JP_ObservationDentalCategory_VSより選択する、必須項目</t>
   </si>
   <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationDentalCategory_VS</t>
+  </si>
+  <si>
     <t>Observation.category:third.id</t>
   </si>
   <si>
@@ -993,16 +1002,22 @@
     <t>Observation.category:third.coding.system</t>
   </si>
   <si>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_ObservationDentalCategory_CS</t>
+  </si>
+  <si>
     <t>Observation.category:third.coding.version</t>
   </si>
   <si>
     <t>Observation.category:third.coding.code</t>
   </si>
   <si>
+    <t>DO-1-01</t>
+  </si>
+  <si>
     <t>Observation.category:third.coding.display</t>
   </si>
   <si>
-    <t>Tooth Existence</t>
+    <t>ToothExistence</t>
   </si>
   <si>
     <t>Observation.category:third.coding.userSelected</t>
@@ -1261,6 +1276,9 @@
   </si>
   <si>
     <t>観測は値を持つように存在しますが、それが誤っている場合、または観測のグループを表す場合はそうではありません。 / An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DentalFundamentalStatus_VS</t>
   </si>
   <si>
     <t xml:space="preserve">obs-7
@@ -1369,10 +1387,7 @@
 2.厚生労働省標準標準歯式マスタ、レセプト電算処理用コード</t>
   </si>
   <si>
-    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DentalBodySite_VS</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1628,7 +1643,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_DentalOral_ToothTreatmentCondition|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_DentalOral_MissingToothCondition)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|QuestionnaireResponse|MolecularSequence)
 </t>
   </si>
   <si>
@@ -4766,7 +4781,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>94</v>
@@ -4800,7 +4815,7 @@
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>83</v>
+        <v>243</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>83</v>
@@ -4842,7 +4857,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4863,10 +4878,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -4877,10 +4892,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4906,13 +4921,13 @@
         <v>212</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4962,7 +4977,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4983,10 +4998,10 @@
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -4997,10 +5012,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5026,21 +5041,21 @@
         <v>114</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>83</v>
+        <v>260</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>83</v>
@@ -5082,7 +5097,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5103,10 +5118,10 @@
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -5117,10 +5132,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5146,14 +5161,14 @@
         <v>212</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5202,7 +5217,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5223,10 +5238,10 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
@@ -5237,10 +5252,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5263,19 +5278,19 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5324,7 +5339,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5345,10 +5360,10 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
@@ -5359,10 +5374,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5388,16 +5403,16 @@
         <v>212</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>83</v>
@@ -5446,7 +5461,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5467,10 +5482,10 @@
         <v>83</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>83</v>
@@ -5481,13 +5496,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>83</v>
@@ -5512,10 +5527,10 @@
         <v>198</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>209</v>
@@ -5603,7 +5618,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>211</v>
@@ -5721,7 +5736,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>218</v>
@@ -5841,7 +5856,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>224</v>
@@ -5963,7 +5978,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>234</v>
@@ -6081,7 +6096,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>236</v>
@@ -6201,7 +6216,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>238</v>
@@ -6246,7 +6261,7 @@
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>83</v>
@@ -6288,7 +6303,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6309,10 +6324,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6323,10 +6338,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6352,13 +6367,13 @@
         <v>212</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6408,7 +6423,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6429,10 +6444,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6443,10 +6458,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6472,21 +6487,21 @@
         <v>114</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>83</v>
@@ -6528,7 +6543,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6549,10 +6564,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6563,10 +6578,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6592,14 +6607,14 @@
         <v>212</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6609,7 +6624,7 @@
         <v>83</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>83</v>
@@ -6648,7 +6663,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6669,10 +6684,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -6683,10 +6698,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6709,19 +6724,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -6770,7 +6785,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6791,10 +6806,10 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -6805,10 +6820,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6834,16 +6849,16 @@
         <v>212</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -6892,7 +6907,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6913,10 +6928,10 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>83</v>
@@ -6927,13 +6942,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>196</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>83</v>
@@ -6958,10 +6973,10 @@
         <v>198</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>209</v>
@@ -6992,11 +7007,11 @@
         <v>83</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>118</v>
+        <v>188</v>
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>202</v>
+        <v>311</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>83</v>
@@ -7049,7 +7064,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>211</v>
@@ -7167,7 +7182,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>218</v>
@@ -7287,7 +7302,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>224</v>
@@ -7409,7 +7424,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>234</v>
@@ -7527,7 +7542,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>236</v>
@@ -7647,7 +7662,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>238</v>
@@ -7658,7 +7673,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>94</v>
@@ -7692,7 +7707,7 @@
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>83</v>
+        <v>318</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>83</v>
@@ -7734,7 +7749,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7755,10 +7770,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7769,10 +7784,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7798,13 +7813,13 @@
         <v>212</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7854,7 +7869,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7875,10 +7890,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7889,10 +7904,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7918,21 +7933,21 @@
         <v>114</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>83</v>
+        <v>321</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>83</v>
@@ -7974,7 +7989,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7995,10 +8010,10 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -8009,10 +8024,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8038,14 +8053,14 @@
         <v>212</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8055,7 +8070,7 @@
         <v>83</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>83</v>
@@ -8094,7 +8109,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8115,10 +8130,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8129,10 +8144,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8155,19 +8170,19 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8216,7 +8231,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8237,10 +8252,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8251,10 +8266,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8280,16 +8295,16 @@
         <v>212</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8338,7 +8353,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8359,10 +8374,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8373,14 +8388,14 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8402,16 +8417,16 @@
         <v>198</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -8436,31 +8451,31 @@
         <v>83</v>
       </c>
       <c r="X53" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF53" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>94</v>
@@ -8475,30 +8490,30 @@
         <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8613,10 +8628,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8733,10 +8748,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8762,10 +8777,10 @@
         <v>225</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>228</v>
@@ -8855,10 +8870,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8973,10 +8988,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9093,10 +9108,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9138,7 +9153,7 @@
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="S59" t="s" s="2">
         <v>83</v>
@@ -9180,7 +9195,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9201,10 +9216,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9215,10 +9230,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9244,13 +9259,13 @@
         <v>212</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9300,7 +9315,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9321,10 +9336,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9335,10 +9350,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9364,21 +9379,21 @@
         <v>114</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q61" s="2"/>
       <c r="R61" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="S61" t="s" s="2">
         <v>83</v>
@@ -9420,7 +9435,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9441,10 +9456,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9455,10 +9470,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9484,14 +9499,14 @@
         <v>212</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9501,7 +9516,7 @@
         <v>83</v>
       </c>
       <c r="S62" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="T62" t="s" s="2">
         <v>83</v>
@@ -9540,7 +9555,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9561,10 +9576,10 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9575,10 +9590,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9601,19 +9616,19 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9662,7 +9677,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9683,10 +9698,10 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9697,10 +9712,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9726,16 +9741,16 @@
         <v>212</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9784,7 +9799,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9805,10 +9820,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9819,10 +9834,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9845,19 +9860,19 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
@@ -9906,7 +9921,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9921,19 +9936,19 @@
         <v>106</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -9941,10 +9956,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9967,7 +9982,7 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="L66" t="s" s="2">
         <v>179</v>
@@ -9976,7 +9991,7 @@
         <v>179</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10026,7 +10041,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10047,13 +10062,13 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10061,14 +10076,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10087,19 +10102,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10148,7 +10163,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10163,19 +10178,19 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
@@ -10183,14 +10198,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10209,19 +10224,19 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -10270,7 +10285,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10285,19 +10300,19 @@
         <v>106</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>
@@ -10305,10 +10320,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10331,16 +10346,16 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10390,7 +10405,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10411,13 +10426,13 @@
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
@@ -10425,10 +10440,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10451,19 +10466,19 @@
         <v>95</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10512,7 +10527,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10527,19 +10542,19 @@
         <v>106</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>83</v>
@@ -10547,10 +10562,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10576,16 +10591,16 @@
         <v>198</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10610,13 +10625,11 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>83</v>
+        <v>407</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -10634,7 +10647,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10643,7 +10656,7 @@
         <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>106</v>
@@ -10652,27 +10665,27 @@
         <v>83</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10698,16 +10711,16 @@
         <v>198</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10732,31 +10745,31 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="Z72" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF72" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10765,7 +10778,7 @@
         <v>94</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>106</v>
@@ -10780,7 +10793,7 @@
         <v>137</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
@@ -10791,14 +10804,14 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10826,10 +10839,10 @@
         <v>179</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -10854,13 +10867,13 @@
         <v>83</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>83</v>
@@ -10878,7 +10891,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10896,27 +10909,27 @@
         <v>83</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10939,7 +10952,7 @@
         <v>83</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="L74" t="s" s="2">
         <v>179</v>
@@ -10948,10 +10961,10 @@
         <v>179</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -11000,7 +11013,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11021,10 +11034,10 @@
         <v>83</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
@@ -11035,10 +11048,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11064,13 +11077,13 @@
         <v>198</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11096,13 +11109,11 @@
         <v>83</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>435</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>83</v>
@@ -11120,7 +11131,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11138,27 +11149,27 @@
         <v>83</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11184,16 +11195,16 @@
         <v>198</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>83</v>
@@ -11218,31 +11229,31 @@
         <v>83</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="Z76" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF76" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11263,10 +11274,10 @@
         <v>83</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
@@ -11277,10 +11288,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11303,7 +11314,7 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="L77" t="s" s="2">
         <v>179</v>
@@ -11312,7 +11323,7 @@
         <v>179</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11362,7 +11373,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11380,27 +11391,27 @@
         <v>83</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11423,16 +11434,16 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11482,7 +11493,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11500,27 +11511,27 @@
         <v>83</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11543,7 +11554,7 @@
         <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="L79" t="s" s="2">
         <v>179</v>
@@ -11552,10 +11563,10 @@
         <v>179</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>83</v>
@@ -11604,7 +11615,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11616,7 +11627,7 @@
         <v>83</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>83</v>
@@ -11625,10 +11636,10 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11639,10 +11650,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11757,10 +11768,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11877,14 +11888,14 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11906,10 +11917,10 @@
         <v>139</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="N82" t="s" s="2">
         <v>156</v>
@@ -11964,7 +11975,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -11999,10 +12010,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12025,13 +12036,13 @@
         <v>83</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12082,7 +12093,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12091,7 +12102,7 @@
         <v>94</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>106</v>
@@ -12103,10 +12114,10 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12117,10 +12128,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12143,13 +12154,13 @@
         <v>83</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12200,7 +12211,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12209,7 +12220,7 @@
         <v>94</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>106</v>
@@ -12221,10 +12232,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12235,10 +12246,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12264,16 +12275,16 @@
         <v>198</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>83</v>
@@ -12301,28 +12312,28 @@
         <v>118</v>
       </c>
       <c r="Y85" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF85" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12340,13 +12351,13 @@
         <v>83</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12357,10 +12368,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12386,16 +12397,16 @@
         <v>198</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -12420,31 +12431,31 @@
         <v>83</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="Y86" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF86" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12462,13 +12473,13 @@
         <v>83</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12479,10 +12490,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12505,17 +12516,17 @@
         <v>83</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
@@ -12564,7 +12575,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12588,7 +12599,7 @@
         <v>83</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>83</v>
@@ -12599,10 +12610,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12628,10 +12639,10 @@
         <v>212</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12682,7 +12693,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12703,10 +12714,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -12717,10 +12728,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12743,16 +12754,16 @@
         <v>95</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12802,7 +12813,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -12823,10 +12834,10 @@
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -12837,10 +12848,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12863,7 +12874,7 @@
         <v>95</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="L90" t="s" s="2">
         <v>179</v>
@@ -12872,7 +12883,7 @@
         <v>179</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12922,7 +12933,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -12943,10 +12954,10 @@
         <v>83</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -12957,10 +12968,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12983,7 +12994,7 @@
         <v>95</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="L91" t="s" s="2">
         <v>179</v>
@@ -12992,10 +13003,10 @@
         <v>179</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13044,7 +13055,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13065,10 +13076,10 @@
         <v>83</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
@@ -13079,10 +13090,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13197,10 +13208,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13317,14 +13328,14 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13346,10 +13357,10 @@
         <v>139</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>156</v>
@@ -13404,7 +13415,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13439,10 +13450,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13468,16 +13479,16 @@
         <v>198</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -13502,13 +13513,13 @@
         <v>83</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>83</v>
@@ -13526,7 +13537,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>94</v>
@@ -13544,16 +13555,16 @@
         <v>83</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>83</v>
@@ -13561,10 +13572,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13587,19 +13598,19 @@
         <v>95</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>83</v>
@@ -13648,7 +13659,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -13666,27 +13677,27 @@
         <v>83</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13712,16 +13723,16 @@
         <v>198</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>83</v>
@@ -13746,13 +13757,13 @@
         <v>83</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>83</v>
@@ -13770,7 +13781,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -13779,7 +13790,7 @@
         <v>94</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>106</v>
@@ -13794,7 +13805,7 @@
         <v>137</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>83</v>
@@ -13805,14 +13816,14 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -13834,16 +13845,16 @@
         <v>198</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>83</v>
@@ -13868,13 +13879,13 @@
         <v>83</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>83</v>
@@ -13892,7 +13903,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -13910,27 +13921,27 @@
         <v>83</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13956,16 +13967,16 @@
         <v>84</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>83</v>
@@ -14014,7 +14025,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14035,10 +14046,10 @@
         <v>83</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>83</v>
